--- a/Result/profitability/2611.xlsx
+++ b/Result/profitability/2611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1087500000000001</v>
+        <v>0.1462500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>29.23875</v>
+        <v>30.16</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04500000000000008</v>
+        <v>0.1462500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>29.475</v>
+        <v>28.92875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07375000000000009</v>
+        <v>0.2150000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>26.77375</v>
+        <v>26.41375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1700000000000001</v>
+        <v>0.2275000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>32.82875</v>
+        <v>32.59</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1562500000000001</v>
+        <v>0.1425000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>32.73875</v>
+        <v>33.15125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02250000000000008</v>
+        <v>0.0825000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>32.62125</v>
+        <v>31.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01249999999999992</v>
+        <v>0.03000000000000008</v>
       </c>
       <c r="N8" t="n">
-        <v>29.245</v>
+        <v>29.57</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>270</v>
+      </c>
+      <c r="D75" t="n">
+        <v>192</v>
+      </c>
+      <c r="E75" t="n">
+        <v>79</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>121</v>
+      </c>
+      <c r="J75" t="n">
+        <v>141</v>
+      </c>
+      <c r="K75" t="n">
+        <v>117</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1937500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.5975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.599999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09807619766125986</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06157317859445521</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
